--- a/administrative_forms/043_technology_maintenance_checklist--administrative_forms.xlsx
+++ b/administrative_forms/043_technology_maintenance_checklist--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>preventative_maintenance</t>
+          <t>on-demand_maintenance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Preventative Maintenance</t>
+          <t>On-demand Maintenance</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>on-demand_maintenance</t>
+          <t>corrective_maintenance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>On-demand Maintenance</t>
+          <t>Corrective Maintenance</t>
         </is>
       </c>
     </row>
@@ -882,29 +882,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>corrective_maintenance</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corrective Maintenance</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>maintenance_type_choices</t>
+          <t>maintenance_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Not started</t>
         </is>
       </c>
     </row>
@@ -967,29 +967,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>deferred</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Deferred</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>maintenance_status_choices</t>
+          <t>maintenance_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deferred</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>semi-annually</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Semi-annually</t>
         </is>
       </c>
     </row>
@@ -1069,27 +1069,10 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>semi-annually</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
-        <is>
-          <t>Semi-annually</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>maintenance_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
         <is>
           <t>Annually</t>
         </is>
